--- a/branches/deps/mii-2027-ballot/ValueSet-mii-vs-molgen-family-member-snomed.xlsx
+++ b/branches/deps/mii-2027-ballot/ValueSet-mii-vs-molgen-family-member-snomed.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-13T12:33:02+00:00</t>
+    <t>2026-09-13T15:32:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
